--- a/salidas/empresas/GEV.xlsx
+++ b/salidas/empresas/GEV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B2" t="n">
-        <v>136.1745300292969</v>
+        <v>136.174560546875</v>
       </c>
       <c r="C2" t="n">
         <v>136.75</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B3" t="n">
-        <v>153.0631866455078</v>
+        <v>153.0631713867188</v>
       </c>
       <c r="C3" t="n">
         <v>153.7100067138672</v>
@@ -526,11 +538,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B4" t="n">
-        <v>175.1597900390625</v>
+        <v>175.1597747802734</v>
       </c>
       <c r="C4" t="n">
         <v>175.8999938964844</v>
@@ -551,11 +563,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>170.7882690429688</v>
+        <v>170.7882537841797</v>
       </c>
       <c r="C5" t="n">
         <v>171.5099945068359</v>
@@ -576,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B6" t="n">
@@ -601,11 +613,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B7" t="n">
-        <v>200.1541900634766</v>
+        <v>200.1541748046875</v>
       </c>
       <c r="C7" t="n">
         <v>201</v>
@@ -626,11 +638,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B8" t="n">
-        <v>253.9070281982422</v>
+        <v>253.9070129394531</v>
       </c>
       <c r="C8" t="n">
         <v>254.9799957275391</v>
@@ -651,7 +663,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B9" t="n">
@@ -676,11 +688,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B10" t="n">
-        <v>332.7139587402344</v>
+        <v>332.7140197753906</v>
       </c>
       <c r="C10" t="n">
         <v>334.1199951171875</v>
@@ -701,11 +713,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B11" t="n">
-        <v>327.7920837402344</v>
+        <v>327.7920532226562</v>
       </c>
       <c r="C11" t="n">
         <v>328.9299926757812</v>
@@ -726,11 +738,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B12" t="n">
-        <v>371.5900268554688</v>
+        <v>371.5900573730469</v>
       </c>
       <c r="C12" t="n">
         <v>372.8800048828125</v>
@@ -751,7 +763,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B13" t="n">
@@ -776,11 +788,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B14" t="n">
-        <v>304.223876953125</v>
+        <v>304.2239074707031</v>
       </c>
       <c r="C14" t="n">
         <v>305.2799987792969</v>
@@ -801,7 +813,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B15" t="n">
@@ -830,11 +842,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B16" t="n">
-        <v>471.7030944824219</v>
+        <v>471.703125</v>
       </c>
       <c r="C16" t="n">
         <v>472.9800109863281</v>
@@ -859,7 +871,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B17" t="n">
@@ -888,7 +900,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B18" t="n">
@@ -917,11 +929,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B19" t="n">
-        <v>611.5811767578125</v>
+        <v>611.5812377929688</v>
       </c>
       <c r="C19" t="n">
         <v>612.969970703125</v>
@@ -946,11 +958,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>613.5068969726562</v>
+        <v>613.5069580078125</v>
       </c>
       <c r="C20" t="n">
         <v>614.9000244140625</v>
@@ -975,7 +987,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B21" t="n">
@@ -1004,7 +1016,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B22" t="n">
@@ -1033,11 +1045,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B23" t="n">
-        <v>652.361083984375</v>
+        <v>652.3611450195312</v>
       </c>
       <c r="C23" t="n">
         <v>653.5700073242188</v>
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B24" t="n">
@@ -1091,7 +1103,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B25" t="n">
@@ -1120,7 +1132,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B26" t="n">
@@ -1149,7 +1161,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B27" t="n">
@@ -1178,7 +1190,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B28" t="n">
@@ -1207,7 +1219,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B29" t="n">
@@ -1236,7 +1248,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B30" t="n">
@@ -1265,7 +1277,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B31" t="n">
@@ -1294,32 +1306,32 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B32" t="n">
-        <v>951.8200073242188</v>
+        <v>955.0399780273438</v>
       </c>
       <c r="C32" t="n">
-        <v>951.8200073242188</v>
+        <v>955.0399780273438</v>
       </c>
       <c r="D32" t="n">
-        <v>36454200</v>
+        <v>38137200</v>
       </c>
       <c r="E32" t="n">
         <v>34.83000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>27.32759136733329</v>
+        <v>27.42003956437966</v>
       </c>
       <c r="G32" t="n">
         <v>266333581</v>
       </c>
       <c r="H32" t="n">
-        <v>253501631018.1054</v>
+        <v>254359217346.1838</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1368742156476317</v>
+        <v>0.1431933587075525</v>
       </c>
     </row>
   </sheetData>
@@ -1351,75 +1363,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -1455,13 +1467,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -1497,13 +1509,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -1539,13 +1551,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -1572,7 +1584,7 @@
       <c r="I5" t="n">
         <v>-0.921021897810219</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K5" t="n">
@@ -1585,13 +1597,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1618,7 +1630,7 @@
       <c r="I6" t="n">
         <v>4.278978102189781</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K6" t="n">
@@ -1631,13 +1643,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1664,7 +1676,7 @@
       <c r="I7" t="n">
         <v>4.548978102189782</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K7" t="n">
@@ -1677,13 +1689,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1710,7 +1722,7 @@
       <c r="I8" t="n">
         <v>5.571007194244605</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K8" t="n">
@@ -1723,13 +1735,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1756,7 +1768,7 @@
       <c r="I9" t="n">
         <v>6.951007194244605</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K9" t="n">
@@ -1769,13 +1781,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1802,7 +1814,7 @@
       <c r="I10" t="n">
         <v>4.161007194244604</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="K10" t="n">
@@ -1815,13 +1827,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1848,7 +1860,7 @@
       <c r="I11" t="n">
         <v>6.151007194244604</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="K11" t="n">
@@ -1861,13 +1873,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1894,7 +1906,7 @@
       <c r="I12" t="n">
         <v>17.69</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K12" t="n">
@@ -1907,13 +1919,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1940,7 +1952,7 @@
       <c r="I13" t="n">
         <v>34.22</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="K13" t="n">
@@ -1953,13 +1965,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1986,7 +1998,7 @@
       <c r="I14" t="n">
         <v>34.83000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="K14" t="n">
@@ -2023,52 +2035,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C2" t="n">
@@ -2097,10 +2109,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45490</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C3" t="n">
@@ -2129,10 +2141,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45581</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C4" t="n">
@@ -2161,10 +2173,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45672</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C5" t="n">
@@ -2193,10 +2205,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C6" t="n">
@@ -2225,10 +2237,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="C7" t="n">
@@ -2257,10 +2269,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="C8" t="n">
@@ -2289,10 +2301,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C9" t="n">
@@ -2321,10 +2333,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="C10" t="n">
@@ -2353,10 +2365,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="C11" t="n">
@@ -2403,12 +2415,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/GEV.xlsx
+++ b/salidas/empresas/GEV.xlsx
@@ -498,7 +498,7 @@
         <v>45382</v>
       </c>
       <c r="B2" t="n">
-        <v>136.174560546875</v>
+        <v>136.1745452880859</v>
       </c>
       <c r="C2" t="n">
         <v>136.75</v>
@@ -517,7 +517,7 @@
         <v>45412</v>
       </c>
       <c r="B3" t="n">
-        <v>153.0631713867188</v>
+        <v>153.0632019042969</v>
       </c>
       <c r="C3" t="n">
         <v>153.7100067138672</v>
@@ -542,7 +542,7 @@
         <v>45443</v>
       </c>
       <c r="B4" t="n">
-        <v>175.1597747802734</v>
+        <v>175.1597900390625</v>
       </c>
       <c r="C4" t="n">
         <v>175.8999938964844</v>
@@ -567,7 +567,7 @@
         <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>170.7882537841797</v>
+        <v>170.7882843017578</v>
       </c>
       <c r="C5" t="n">
         <v>171.5099945068359</v>
@@ -592,7 +592,7 @@
         <v>45504</v>
       </c>
       <c r="B6" t="n">
-        <v>177.4899749755859</v>
+        <v>177.4899597167969</v>
       </c>
       <c r="C6" t="n">
         <v>178.2400054931641</v>
@@ -617,7 +617,7 @@
         <v>45535</v>
       </c>
       <c r="B7" t="n">
-        <v>200.1541748046875</v>
+        <v>200.1541900634766</v>
       </c>
       <c r="C7" t="n">
         <v>201</v>
@@ -692,7 +692,7 @@
         <v>45626</v>
       </c>
       <c r="B10" t="n">
-        <v>332.7140197753906</v>
+        <v>332.7140502929688</v>
       </c>
       <c r="C10" t="n">
         <v>334.1199951171875</v>
@@ -846,7 +846,7 @@
         <v>45808</v>
       </c>
       <c r="B16" t="n">
-        <v>471.703125</v>
+        <v>471.7030944824219</v>
       </c>
       <c r="C16" t="n">
         <v>472.9800109863281</v>
@@ -904,7 +904,7 @@
         <v>45869</v>
       </c>
       <c r="B18" t="n">
-        <v>658.7940063476562</v>
+        <v>658.7940673828125</v>
       </c>
       <c r="C18" t="n">
         <v>660.2899780273438</v>
